--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-ips-immunization.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-ips-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-16T10:23:49+00:00</t>
+    <t>2025-01-15T11:57:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-ips-immunization.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-ips-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-15T11:57:38+00:00</t>
+    <t>2025-01-29T12:25:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
